--- a/tests/fixtures/raw/CP03_bad.xlsx
+++ b/tests/fixtures/raw/CP03_bad.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,11 @@
           <t>적용모델</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>개정일</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -586,6 +591,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -634,6 +644,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -682,6 +697,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="n"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -730,6 +750,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -778,6 +803,11 @@
         </is>
       </c>
       <c r="J8" s="4" t="n"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -826,6 +856,11 @@
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -878,6 +913,11 @@
           <t>M2</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -926,6 +966,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -974,6 +1019,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="n"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1022,6 +1072,11 @@
         </is>
       </c>
       <c r="J13" s="4" t="n"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1070,6 +1125,11 @@
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1098,6 +1158,11 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="4" t="n"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1146,11 +1211,16 @@
         </is>
       </c>
       <c r="J16" s="4" t="n"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
